--- a/inst/pipeline/Template/TEMPLATE_Ab_Titration_Instructions.xlsx
+++ b/inst/pipeline/Template/TEMPLATE_Ab_Titration_Instructions.xlsx
@@ -425,10 +425,10 @@
     <t>tabbed_by</t>
   </si>
   <si>
-    <t>NOT ACTIVE as of v2_86 -- gate_manual is disabled in this version; use an automated gating method instead. Planned to return in a future ACTA release. (When active: applies gates pre-drawn with drawManualGates(), cached per sample -- full user control, fallback when automated gates are unreliable.)</t>
-  </si>
-  <si>
-    <t>NOT ACTIVE as of v2_86 -- do not uncomment this row; gate_manual is disabled in this version. Planned to return in a future ACTA release.</t>
+    <t>NOT IMPLEMENTED -- use an automated gating method. Planned for a future release, not merely switched off: it needs an interactive gating UI that ACTA does not have, because flowGate's drawer launches its own blocking Shiny app and cannot run inside ACTA's. (Design intent: applies gates pre-drawn with drawManualGates(), cached per sample -- full user control, fallback when automated gates are unreliable.)</t>
+  </si>
+  <si>
+    <t>NOT IMPLEMENTED -- do not uncomment this row. Drawing gates by hand needs an interactive gating UI that ACTA does not have; it is planned for a future release, not merely switched off. Use an automated method.</t>
   </si>
   <si>
     <t>flowjo_transformation_arg</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">gate_manual</t>
   </si>
   <si>
-    <t xml:space="preserve">NOT ACTIVE as of v2_86 -- do not uncomment this row; gate_manual is disabled in this version. Planned to return in a future ACTA release.</t>
+    <t xml:space="preserve">NOT IMPLEMENTED -- do not uncomment this row. Drawing gates by hand needs an interactive gating UI that ACTA does not have; it is planned for a future release, not merely switched off. Use an automated method.</t>
   </si>
   <si>
     <t xml:space="preserve">#gate_flowclust_2d</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">(none -- gates come from the drawManualGates() cache; no tunable gating_args)</t>
   </si>
   <si>
-    <t xml:space="preserve">NOT ACTIVE as of v2_86 -- gate_manual is disabled in this version; use an automated gating method instead. Planned to return in a future ACTA release. (When active: applies gates pre-drawn with drawManualGates(), cached per sample -- full user control, fallback when automated gates are unreliable.)</t>
+    <t xml:space="preserve">NOT IMPLEMENTED -- use an automated gating method. Planned for a future release, not merely switched off: it needs an interactive gating UI that ACTA does not have, because flowGate's drawer launches its own blocking Shiny app and cannot run inside ACTA's. (Design intent: applies gates pre-drawn with drawManualGates(), cached per sample -- full user control, fallback when automated gates are unreliable.)</t>
   </si>
 </sst>
 </file>
@@ -2459,42 +2459,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">#CD3</t>
+          <t>#CD3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">+/-</t>
+          <t>+/-</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Live</t>
+          <t>Live</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t xml:space="preserve">CD3, FSC-A</t>
+          <t>CD3, FSC-A</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t xml:space="preserve">gate_flowmeans</t>
+          <t>gate_flowmeans</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t xml:space="preserve">K=2, cluster="neg", quantile=0.99</t>
+          <t>K=2, cluster="neg", quantile=0.99</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t xml:space="preserve">FALSE</t>
+          <t>FALSE</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dirname</t>
+          <t>Dirname</t>
         </is>
       </c>
       <c r="I5"/>
@@ -2503,22 +2503,22 @@
       <c r="L5"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t xml:space="preserve">1D marker gate that keeps BOTH populations. `pop = +/-` makes two nodes, &lt;alias&gt;+ and &lt;alias&gt;- (here CD3+ and CD3-), and either can be a `parent` -- set the Reagent row's parent to CD3+ to titrate inside CD3+. Give TWO dims: the gate is computed on the FIRST one only (gate_flowmeans reads channels[1]), the second is just the plot's y axis. With ONE dim openCyto ignores `alias` and names the nodes after the dim instead (FITC-A+/FITC-A-). `+-` is NOT this -- it means a single quadrant of a 2D gate. `groupBy` only takes effect when collapseDataForGating is TRUE. Uncomment (delete the #) and set `dims` to a marker in your panel.</t>
+          <t>1D marker gate that keeps BOTH populations. `pop = +/-` makes two nodes, &lt;alias&gt;+ and &lt;alias&gt;- (here CD3+ and CD3-), and either can be a `parent` -- set the Reagent row's parent to CD3+ to titrate inside CD3+. Give TWO dims: the gate is computed on the FIRST one only (gate_flowmeans reads channels[1]), the second is just the plot's y axis. With ONE dim openCyto ignores `alias` and names the nodes after the dim instead (FITC-A+/FITC-A-). `+-` is NOT this -- it means a single quadrant of a 2D gate. `groupBy` only takes effect when collapseDataForGating is TRUE. Uncomment (delete the #) and set `dims` to a marker in your panel.</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRUE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRUE</t>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t xml:space="preserve">TRUE</t>
+          <t>TRUE</t>
         </is>
       </c>
     </row>
@@ -2697,65 +2697,112 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="s">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>#Reagent</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>+/-</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Live</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>FSC-A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>gate_flowmeans_costain</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>K=2, cluster='neg', quantile=0.99</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Dirname</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>pp_costain_floor</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>costain_quantile=0.99</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
         <v>265</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>266</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>254</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D11" t="s">
         <v>267</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E11" t="s">
         <v>280</v>
       </c>
-      <c r="F10"/>
-      <c r="G10"/>
-      <c r="H10" t="s">
-        <v>152</v>
-      </c>
-      <c r="I10"/>
-      <c r="J10"/>
-      <c r="K10"/>
-      <c r="L10"/>
-      <c r="M10" t="s">
-        <v>281</v>
-      </c>
-      <c r="N10" t="s">
-        <v>272</v>
-      </c>
-      <c r="O10" t="s">
-        <v>272</v>
-      </c>
-      <c r="P10" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11"/>
-      <c r="B11"/>
-      <c r="C11"/>
-      <c r="D11"/>
-      <c r="E11"/>
       <c r="F11"/>
       <c r="G11"/>
-      <c r="H11"/>
+      <c r="H11" t="s">
+        <v>152</v>
+      </c>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
       <c r="L11"/>
-      <c r="M11"/>
-      <c r="N11"/>
-      <c r="O11"/>
-      <c r="P11"/>
+      <c r="M11" t="s">
+        <v>281</v>
+      </c>
+      <c r="N11" t="s">
+        <v>272</v>
+      </c>
+      <c r="O11" t="s">
+        <v>272</v>
+      </c>
+      <c r="P11" t="s">
+        <v>272</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" t="s">
-        <v>282</v>
-      </c>
+      <c r="A12"/>
       <c r="B12"/>
       <c r="C12"/>
       <c r="D12"/>
@@ -2765,20 +2812,16 @@
       <c r="H12"/>
       <c r="I12"/>
       <c r="J12"/>
-      <c r="K12" t="s">
-        <v>283</v>
-      </c>
+      <c r="K12"/>
       <c r="L12"/>
-      <c r="M12" t="s">
-        <v>284</v>
-      </c>
+      <c r="M12"/>
       <c r="N12"/>
       <c r="O12"/>
       <c r="P12"/>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B13"/>
       <c r="C13"/>
@@ -2790,11 +2833,11 @@
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="L13"/>
       <c r="M13" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="N13"/>
       <c r="O13"/>
@@ -2802,7 +2845,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B14"/>
       <c r="C14"/>
@@ -2814,11 +2857,11 @@
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="L14"/>
       <c r="M14" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="N14"/>
       <c r="O14"/>
@@ -2826,7 +2869,7 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B15"/>
       <c r="C15"/>
@@ -2838,11 +2881,11 @@
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15" t="s">
-        <v>269</v>
+        <v>289</v>
       </c>
       <c r="L15"/>
       <c r="M15" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="N15"/>
       <c r="O15"/>
@@ -2850,7 +2893,7 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="B16"/>
       <c r="C16"/>
@@ -2858,15 +2901,15 @@
       <c r="E16"/>
       <c r="F16"/>
       <c r="G16"/>
-      <c r="H16" s="1"/>
+      <c r="H16"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16" t="s">
-        <v>289</v>
+        <v>269</v>
       </c>
       <c r="L16"/>
       <c r="M16" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="N16"/>
       <c r="O16"/>
@@ -2874,7 +2917,7 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B17"/>
       <c r="C17"/>
@@ -2882,15 +2925,15 @@
       <c r="E17"/>
       <c r="F17"/>
       <c r="G17"/>
-      <c r="H17"/>
+      <c r="H17" s="1"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="L17"/>
       <c r="M17" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="N17"/>
       <c r="O17"/>
@@ -2898,7 +2941,7 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B18"/>
       <c r="C18"/>
@@ -2910,11 +2953,11 @@
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="L18"/>
       <c r="M18" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="N18"/>
       <c r="O18"/>
@@ -2922,7 +2965,7 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B19"/>
       <c r="C19"/>
@@ -2933,12 +2976,12 @@
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19"/>
-      <c r="K19"/>
-      <c r="L19" t="s">
-        <v>271</v>
-      </c>
+      <c r="K19" t="s">
+        <v>289</v>
+      </c>
+      <c r="L19"/>
       <c r="M19" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="N19"/>
       <c r="O19"/>
@@ -2946,7 +2989,7 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B20"/>
       <c r="C20"/>
@@ -2959,10 +3002,10 @@
       <c r="J20"/>
       <c r="K20"/>
       <c r="L20" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="M20" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="N20"/>
       <c r="O20"/>
@@ -2970,7 +3013,7 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B21"/>
       <c r="C21"/>
@@ -2981,12 +3024,12 @@
       <c r="H21"/>
       <c r="I21"/>
       <c r="J21"/>
-      <c r="K21" t="s">
-        <v>304</v>
-      </c>
-      <c r="L21"/>
+      <c r="K21"/>
+      <c r="L21" t="s">
+        <v>277</v>
+      </c>
       <c r="M21" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="N21"/>
       <c r="O21"/>
@@ -2994,7 +3037,7 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="B22"/>
       <c r="C22"/>
@@ -3006,11 +3049,11 @@
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="L22"/>
       <c r="M22" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="N22"/>
       <c r="O22"/>
@@ -3018,7 +3061,7 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="B23"/>
       <c r="C23"/>
@@ -3030,11 +3073,11 @@
       <c r="I23"/>
       <c r="J23"/>
       <c r="K23" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="L23"/>
       <c r="M23" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="N23"/>
       <c r="O23"/>
@@ -3042,7 +3085,7 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="B24"/>
       <c r="C24"/>
@@ -3054,11 +3097,11 @@
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="L24"/>
       <c r="M24" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="N24"/>
       <c r="O24"/>
@@ -3066,7 +3109,7 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B25"/>
       <c r="C25"/>
@@ -3078,11 +3121,11 @@
       <c r="I25"/>
       <c r="J25"/>
       <c r="K25" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="L25"/>
       <c r="M25" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="N25"/>
       <c r="O25"/>
@@ -3090,7 +3133,7 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="B26"/>
       <c r="C26"/>
@@ -3102,15 +3145,39 @@
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="L26"/>
       <c r="M26" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="N26"/>
       <c r="O26"/>
       <c r="P26"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>318</v>
+      </c>
+      <c r="B27"/>
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27"/>
+      <c r="K27" t="s">
+        <v>319</v>
+      </c>
+      <c r="L27"/>
+      <c r="M27" t="s">
+        <v>320</v>
+      </c>
+      <c r="N27"/>
+      <c r="O27"/>
+      <c r="P27"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
